--- a/Master.xlsx
+++ b/Master.xlsx
@@ -529,23 +529,26 @@
       <c r="AE1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>Prakhar</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>prakharvasishtha9@gmail.com</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -560,23 +563,26 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Sonam</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>sonampvasishtha@gmail.com</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>

--- a/Master.xlsx
+++ b/Master.xlsx
@@ -539,16 +539,15 @@
           <t>Prakhar</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>prakharvasishtha9@gmail.com</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -573,16 +572,15 @@
           <t>Sonam</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>sonampvasishtha@gmail.com</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
